--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\rom-folderer\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kertis/Code/rom-folderer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC6257B-9C7E-4552-9746-5C4C6436FD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8030312-25FE-8347-8EAB-FB674470D9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19320" yWindow="4770" windowWidth="24750" windowHeight="17355" xr2:uid="{09D53552-1463-4F16-9BD4-A353FB5A1398}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="1" xr2:uid="{09D53552-1463-4F16-9BD4-A353FB5A1398}"/>
   </bookViews>
   <sheets>
     <sheet name="Systems" sheetId="1" r:id="rId1"/>
@@ -900,9 +900,6 @@
     <t>GBC</t>
   </si>
   <si>
-    <t>PCE</t>
-  </si>
-  <si>
     <t>GG</t>
   </si>
   <si>
@@ -915,9 +912,6 @@
     <t>NEOCD</t>
   </si>
   <si>
-    <t>PCECD</t>
-  </si>
-  <si>
     <t>DOS</t>
   </si>
   <si>
@@ -934,6 +928,12 @@
   </si>
   <si>
     <t>7800,a7800,atari7800</t>
+  </si>
+  <si>
+    <t>pcengine</t>
+  </si>
+  <si>
+    <t>pcenginecd</t>
   </si>
 </sst>
 </file>
@@ -1332,13 +1332,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F045E33-1671-4698-A15E-5993233E5D1E}">
   <dimension ref="A1:B164"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="47.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>168</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>165</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>164</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>163</v>
       </c>
@@ -1386,17 +1386,17 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>160</v>
       </c>
@@ -1404,17 +1404,17 @@
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>158</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>157</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>155</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>156</v>
       </c>
@@ -1446,39 +1446,39 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>154</v>
       </c>
       <c r="B18" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>149</v>
       </c>
@@ -1518,37 +1518,37 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>142</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>141</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>140</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>139</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>138</v>
       </c>
@@ -1596,17 +1596,17 @@
         <v>267</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>135</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>134</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -1630,65 +1630,65 @@
         <v>266</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>122</v>
       </c>
@@ -1696,32 +1696,32 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -1729,17 +1729,17 @@
         <v>214</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>113</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>112</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>110</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>109</v>
       </c>
@@ -1771,17 +1771,17 @@
         <v>226</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>106</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -1797,32 +1797,32 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>99</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>98</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>97</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>96</v>
       </c>
@@ -1854,27 +1854,27 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>28</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>2</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>13</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>87</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>86</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>84</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>82</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>81</v>
       </c>
@@ -2026,37 +2026,37 @@
         <v>256</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>72</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>71</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>74</v>
       </c>
@@ -2088,12 +2088,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>283</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>66</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>19</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>25</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>65</v>
       </c>
@@ -2133,12 +2133,12 @@
         <v>205</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>21</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>12</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>63</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>60</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>62</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>61</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>59</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>58</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>57</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>56</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>55</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>22</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>68</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>53</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>52</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>51</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>50</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>49</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>48</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>27</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>54</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>47</v>
       </c>
@@ -2346,12 +2346,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>44</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>43</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>42</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>41</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>39</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>45</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>38</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>37</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>36</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>230</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>34</v>
       </c>
@@ -2463,12 +2463,12 @@
         <v>229</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>31</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>33</v>
       </c>
@@ -2484,12 +2484,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>29</v>
       </c>
@@ -2506,14 +2506,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1930EB-6B5A-4138-8372-6C9155206B66}">
   <dimension ref="A1:C185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>275</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>275</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>275</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>275</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>275</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>275</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>275</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>275</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>275</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>275</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>275</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>275</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>275</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>275</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>275</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>275</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>275</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>275</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>275</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>275</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>275</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>275</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>275</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>275</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>275</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>275</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>275</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>275</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>275</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>275</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>275</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>275</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>275</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>275</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>275</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>275</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>275</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>275</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>275</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>275</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>275</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>275</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>275</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>275</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>275</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>275</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>275</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>275</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>275</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>275</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>275</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>275</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>275</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>275</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>275</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>275</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>275</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>275</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>275</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>275</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>275</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>275</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>275</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>275</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>275</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>275</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>275</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>275</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>275</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>275</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>275</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>275</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>275</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>275</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>275</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>275</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>275</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>275</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>275</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>275</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>275</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>275</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>275</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>275</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>275</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>275</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>275</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>275</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>275</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>275</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>275</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>275</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>275</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>275</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>275</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>275</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>275</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>275</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>275</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>275</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>275</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>275</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>275</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>275</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>275</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>275</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>275</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>275</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>275</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>275</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>275</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>275</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>275</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>275</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>275</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>275</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>275</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>275</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>275</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>275</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>275</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>275</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>275</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>275</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>275</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>275</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>275</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>275</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>275</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>275</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>275</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>275</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>275</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>275</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>275</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>275</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>275</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>275</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>275</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>275</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>275</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>275</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>275</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>275</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>275</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>275</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>275</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>275</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>275</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>275</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>275</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>275</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>275</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>275</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>275</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>275</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>275</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>275</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>275</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -4372,18 +4372,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>7</v>
       </c>
       <c r="B170" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C170" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -4479,10 +4479,10 @@
         <v>17</v>
       </c>
       <c r="C179" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -4490,10 +4490,10 @@
         <v>21</v>
       </c>
       <c r="C180" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -4501,10 +4501,10 @@
         <v>27</v>
       </c>
       <c r="C181" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -4512,10 +4512,10 @@
         <v>19</v>
       </c>
       <c r="C182" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>7</v>
       </c>
@@ -4523,10 +4523,10 @@
         <v>22</v>
       </c>
       <c r="C183" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>7</v>
       </c>
@@ -4534,18 +4534,18 @@
         <v>23</v>
       </c>
       <c r="C184" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>7</v>
       </c>
       <c r="B185" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C185" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
